--- a/PWA TEST CASE.xlsx
+++ b/PWA TEST CASE.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCAA8BCE-9534-4FDE-BDEC-7F3E4ADA617C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4226A4-5EA7-4E9C-A6E0-E0788434EE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{B3D6F52D-9382-4FC2-8F8A-E2EC789D73AA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{B3D6F52D-9382-4FC2-8F8A-E2EC789D73AA}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="PWA&amp;PS" sheetId="1" r:id="rId1"/>
+    <sheet name="ANDROID TEST" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="179">
   <si>
     <t>TC ID</t>
   </si>
@@ -61,6 +63,9 @@
   </si>
   <si>
     <t>MK-LOGIN-001</t>
+  </si>
+  <si>
+    <t>Login</t>
   </si>
   <si>
     <t>Forgot Password / OTP</t>
@@ -88,9 +93,6 @@
   </si>
   <si>
     <t>RESULT</t>
-  </si>
-  <si>
-    <t>FAILED</t>
   </si>
   <si>
     <t>Product Images</t>
@@ -235,6 +237,9 @@
     <t>Screenshot</t>
   </si>
   <si>
+    <t>Test Steps</t>
+  </si>
+  <si>
     <t>QA-LOGIN-009</t>
   </si>
   <si>
@@ -274,6 +279,9 @@
     <t>MK-PROF-001</t>
   </si>
   <si>
+    <t>Profile</t>
+  </si>
+  <si>
     <t>Use Current Location</t>
   </si>
   <si>
@@ -289,6 +297,9 @@
     <t>Error message "Could not retrieve your current location" is displayed. Address fields contain invalid/default values such as N/A, Unknown, 000000</t>
   </si>
   <si>
+    <t>Attached</t>
+  </si>
+  <si>
     <t>User cannot update address using current location</t>
   </si>
   <si>
@@ -299,13 +310,389 @@
   </si>
   <si>
     <t>Catalog-PWA</t>
+  </si>
+  <si>
+    <t>SAISREE</t>
+  </si>
+  <si>
+    <t>MK-PO-001</t>
+  </si>
+  <si>
+    <t>Quantity Display</t>
+  </si>
+  <si>
+    <t>Verify quantity is fully visible in purchase order item grid</t>
+  </si>
+  <si>
+    <t>Product: TOOR DAL, Qty: 50 KGS</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quantity field should clearly display </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Quantity field width is too small; only part of the value is visible, making it appear as </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> instead of </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>50</t>
+    </r>
+  </si>
+  <si>
+    <t>User may misinterpret quantity and create incorrect purchase orders</t>
+  </si>
+  <si>
+    <t>POS-Purchase Orders</t>
+  </si>
+  <si>
+    <t>NOT FIXED</t>
+  </si>
+  <si>
+    <t>Refresh</t>
+  </si>
+  <si>
+    <t>LOGIN-004</t>
+  </si>
+  <si>
+    <t>HOME-005</t>
+  </si>
+  <si>
+    <t>Home</t>
+  </si>
+  <si>
+    <t>Verify Home Screen refresh functionality</t>
+  </si>
+  <si>
+    <t>PROF-UI-001</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>PROF-004</t>
+  </si>
+  <si>
+    <t>Profile View</t>
+  </si>
+  <si>
+    <t>Verify Profile page displays user details correctly</t>
+  </si>
+  <si>
+    <t>Profile page exists, but user details and account management options are missing or not visible.</t>
+  </si>
+  <si>
+    <t>UI-NAV-003</t>
+  </si>
+  <si>
+    <t>Verify application footer navigation is displayed on Profile/Login screen</t>
+  </si>
+  <si>
+    <t>LOGIN-006</t>
+  </si>
+  <si>
+    <t>Login screen should contain only Login, Register, Forgot Password, and authentication-related controls.</t>
+  </si>
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>Issue</t>
+  </si>
+  <si>
+    <t>Password field does not show a Show/Hide Eye icon. Users cannot verify the entered password.</t>
+  </si>
+  <si>
+    <t>MK-LOGIN-002</t>
+  </si>
+  <si>
+    <t>No “Forgot Password?” link is visible below the password field. Users may not know how to reset the password.</t>
+  </si>
+  <si>
+    <t>MK-LOGIN-003</t>
+  </si>
+  <si>
+    <t>Phone Number field does not indicate validation requirements such as 10 digits and numeric only.</t>
+  </si>
+  <si>
+    <t>MK-LOGIN-004</t>
+  </si>
+  <si>
+    <t>Login tab and Login button both display the same text, which may confuse users.</t>
+  </si>
+  <si>
+    <t>MK-PROF-005</t>
+  </si>
+  <si>
+    <t>No loading indicator/spinner during login process. Multiple taps may create duplicate requests.</t>
+  </si>
+  <si>
+    <t>MK-PROF-006</t>
+  </si>
+  <si>
+    <t>No error message area visible for invalid credentials.</t>
+  </si>
+  <si>
+    <t>MK-PROF-007</t>
+  </si>
+  <si>
+    <t>Placeholder text is very light and may have low visibility on some devices.</t>
+  </si>
+  <si>
+    <t>MK-PROF-008</t>
+  </si>
+  <si>
+    <t>Input fields appear too tall, resulting in excessive whitespace on smaller screens.</t>
+  </si>
+  <si>
+    <t>MK-PROF-009</t>
+  </si>
+  <si>
+    <t>Password keyboard type may not be optimized (needs secure password keyboard).</t>
+  </si>
+  <si>
+    <t>Medium Priority Issues</t>
+  </si>
+  <si>
+    <t>High Priority Issues</t>
+  </si>
+  <si>
+    <t>UX Improvements</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Suggestion</t>
+  </si>
+  <si>
+    <t>UX-001</t>
+  </si>
+  <si>
+    <t>Add Phone icon in Phone Number field.</t>
+  </si>
+  <si>
+    <t>UX-002</t>
+  </si>
+  <si>
+    <t>Add Lock icon in Password field.</t>
+  </si>
+  <si>
+    <t>UX-003</t>
+  </si>
+  <si>
+    <t>Add Eye/Eye-Off icon in Password field.</t>
+  </si>
+  <si>
+    <t>UX-004</t>
+  </si>
+  <si>
+    <t>Add "Forgot Password?" link below password field.</t>
+  </si>
+  <si>
+    <t>UX-005</t>
+  </si>
+  <si>
+    <t>Show app version at bottom (e.g., v1.0.0).</t>
+  </si>
+  <si>
+    <t>UX-006</t>
+  </si>
+  <si>
+    <t>Show Help Center / Contact Support in footer instead of a separate card.</t>
+  </si>
+  <si>
+    <t>UX-007</t>
+  </si>
+  <si>
+    <t>Add Terms &amp; Privacy links in footer.</t>
+  </si>
+  <si>
+    <t>Branding Logo</t>
+  </si>
+  <si>
+    <t>Verify Mana Kirana logo is displayed on Login screen</t>
+  </si>
+  <si>
+    <t>Verify user can show and hide the password using the Eye icon</t>
+  </si>
+  <si>
+    <t>1. Open Login Screen.2. Enter a password.3. Click the Eye icon.4. Verify password visibility.5. Click again.6. Verify password is hidden.</t>
+  </si>
+  <si>
+    <t>Password should toggle between visible and masked states.</t>
+  </si>
+  <si>
+    <t>Eye icon is missing; users cannot show or hide the password.</t>
+  </si>
+  <si>
+    <t>1. Login to the application.2. Navigate to Profile/My Account page.3. Observe profile details.</t>
+  </si>
+  <si>
+    <t>User Name, Mobile Number, Email Address, Profile Picture, My Orders, Delivery Addresses, Help &amp; Support, and Logout should be displayed.</t>
+  </si>
+  <si>
+    <t>Profile Layout</t>
+  </si>
+  <si>
+    <t>Verify Profile page displays a structured e-commerce profile layout</t>
+  </si>
+  <si>
+    <t>1. Login to the application.2. Open Profile page.3. Verify layout and menu structure.</t>
+  </si>
+  <si>
+    <t>Profile page should display user information, quick actions, and support options in a structured layout.</t>
+  </si>
+  <si>
+    <t>Profile page layout is incomplete and does not follow standard e-commerce profile design.</t>
+  </si>
+  <si>
+    <t>1. Login to the application.2. Navigate to Home Screen.3. Click Refresh or perform pull-to-refresh.4. Observe data updates.</t>
+  </si>
+  <si>
+    <t>Home screen should reload and fetch the latest dashboard, catalog, and order data.</t>
+  </si>
+  <si>
+    <t>Refresh action does not reload the screen or update displayed data.</t>
+  </si>
+  <si>
+    <t>Navigation</t>
+  </si>
+  <si>
+    <t>Footer Navigation</t>
+  </si>
+  <si>
+    <t>1. Open the application.2. Navigate to Login/Profile screen.3. Observe bottom navigation area.</t>
+  </si>
+  <si>
+    <t>Application footer navigation (Home, Categories, Cart, Orders, Account) should be visible.</t>
+  </si>
+  <si>
+    <t>Footer navigation is not displayed. Only Android system navigation buttons are visible.</t>
+  </si>
+  <si>
+    <t>Screen Layout</t>
+  </si>
+  <si>
+    <t>Verify only login-related options are displayed on Login screen</t>
+  </si>
+  <si>
+    <t>1. Open Login screen.2. Observe content below login form.</t>
+  </si>
+  <si>
+    <t>My Orders, Delivery Address, and Help &amp; Support sections are displayed on the Login screen, causing unnecessary clutter.</t>
+  </si>
+  <si>
+    <t>LOGIN-009</t>
+  </si>
+  <si>
+    <t>1. Open the application.2. Navigate to Login screen.3. Observe top section.</t>
+  </si>
+  <si>
+    <t>Mana Kirana logo should be displayed prominently at the top of the Login screen.</t>
+  </si>
+  <si>
+    <t>No Mana Kirana logo or branding is displayed on the Login screen.</t>
+  </si>
+  <si>
+    <t>LOC-001</t>
+  </si>
+  <si>
+    <t>Location</t>
+  </si>
+  <si>
+    <t>Delivery Availability</t>
+  </si>
+  <si>
+    <t>Verify unsupported delivery locations display a service availability popup</t>
+  </si>
+  <si>
+    <t>1. Open the application.2. Select or enter a delivery address outside the supported service area.3. Attempt to place an order.</t>
+  </si>
+  <si>
+    <t>System should display a popup stating that delivery service is unavailable in the selected location and prevent order placement.</t>
+  </si>
+  <si>
+    <t>No popup is displayed and users can proceed without knowing delivery is unavailable for that location.</t>
+  </si>
+  <si>
+    <t>Customers from unsupported locations can place orders, leading to order cancellations, customer dissatisfaction, and operational issues.</t>
+  </si>
+  <si>
+    <t>ORD-007</t>
+  </si>
+  <si>
+    <t>Orders</t>
+  </si>
+  <si>
+    <t>Order Cancellation</t>
+  </si>
+  <si>
+    <t>Verify order cancellation captures cancellation remarks/reason</t>
+  </si>
+  <si>
+    <t>1. Open an existing order.2. Click Cancel Order.3. Observe the cancellation screen.</t>
+  </si>
+  <si>
+    <t>System should provide a mandatory Remarks/Reason field before cancelling the order.</t>
+  </si>
+  <si>
+    <t>Order can be cancelled without capturing any cancellation reason or remarks.</t>
+  </si>
+  <si>
+    <t>Capturing cancellation reasons helps with:
+Customer support tracking
+Delivery analysis
+Order cancellation reporting
+Business decision-making
+Audit and operational monitoring</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -316,6 +703,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -342,13 +745,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -669,6 +1085,105 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>86591</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>55102</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2289598</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1216277</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="21" name="Picture 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F23D6B2F-47A8-AA96-9E16-932205C9D559}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14185165" y="8926734"/>
+          <a:ext cx="2203007" cy="1161175"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>111597</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>2743199</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>828710</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DACEBAFB-F096-ECCC-1C37-1B253A9AF8AB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15573375" y="4293072"/>
+          <a:ext cx="2571749" cy="717113"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -969,7 +1484,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFB614DB-3D63-42AB-9BC3-5B614D09FC6D}">
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr defaultRowHeight="99.95" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.28515625" customWidth="1"/>
@@ -1024,13 +1539,13 @@
         <v>10</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1038,38 +1553,44 @@
         <v>11</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>29</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>20</v>
+        <v>54</v>
+      </c>
+      <c r="N2" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1077,7 +1598,7 @@
         <v>28</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="C3" s="2" t="s">
         <v>21</v>
@@ -1095,20 +1616,26 @@
         <v>25</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>26</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
         <v>27</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>20</v>
+        <v>54</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1134,20 +1661,26 @@
         <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2" t="s">
         <v>35</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>20</v>
+        <v>54</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
@@ -1173,114 +1706,771 @@
         <v>43</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
         <v>44</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>20</v>
+        <v>54</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>26</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N6" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="O6" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="O6" s="2" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>63</v>
-      </c>
       <c r="H7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K7" s="2"/>
       <c r="L7" s="2" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>56</v>
-      </c>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L11" s="6"/>
+    </row>
+    <row r="12" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L12" s="6"/>
+    </row>
+    <row r="13" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L13" s="6"/>
+    </row>
+    <row r="14" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L14" s="6"/>
+    </row>
+    <row r="15" spans="1:15" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L15" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
   <drawing r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051ED67A-7A87-42BF-9B2E-79681FD8C52B}">
+  <dimension ref="A1:K8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17" customWidth="1"/>
+    <col min="2" max="2" width="20.42578125" customWidth="1"/>
+    <col min="3" max="3" width="14.42578125" customWidth="1"/>
+    <col min="4" max="4" width="24.42578125" customWidth="1"/>
+    <col min="5" max="5" width="44.42578125" customWidth="1"/>
+    <col min="6" max="6" width="32.85546875" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" customWidth="1"/>
+    <col min="10" max="10" width="40.7109375" customWidth="1"/>
+    <col min="11" max="11" width="43.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="135" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{297F91DC-A724-4E74-ACA4-666ADFBE7D9B}">
+  <dimension ref="A1:C22"/>
+  <sheetFormatPr defaultRowHeight="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21.140625" customWidth="1"/>
+    <col min="2" max="2" width="25.7109375" customWidth="1"/>
+    <col min="3" max="3" width="55.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="4" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/PWA TEST CASE.xlsx
+++ b/PWA TEST CASE.xlsx
@@ -8,16 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC4226A4-5EA7-4E9C-A6E0-E0788434EE84}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F47BD6-5B92-42D3-89C4-061B44126DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{B3D6F52D-9382-4FC2-8F8A-E2EC789D73AA}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="4" xr2:uid="{B3D6F52D-9382-4FC2-8F8A-E2EC789D73AA}"/>
   </bookViews>
   <sheets>
     <sheet name="PWA&amp;PS" sheetId="1" r:id="rId1"/>
     <sheet name="ANDROID TEST" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="login" sheetId="3" r:id="rId3"/>
+    <sheet name="categories" sheetId="4" r:id="rId4"/>
+    <sheet name="Cart" sheetId="7" r:id="rId5"/>
+    <sheet name="PossibleReqirements" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -27,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="233">
   <si>
     <t>TC ID</t>
   </si>
@@ -687,12 +691,174 @@
 Business decision-making
 Audit and operational monitoring</t>
   </si>
+  <si>
+    <t>CAT-001</t>
+  </si>
+  <si>
+    <t>Categories</t>
+  </si>
+  <si>
+    <t>Product names truncated excessively</t>
+  </si>
+  <si>
+    <t>CAT-002</t>
+  </si>
+  <si>
+    <t>Floating cart button overlaps product card</t>
+  </si>
+  <si>
+    <t>CAT-003</t>
+  </si>
+  <si>
+    <t>Category panel width too small causing text wrapping</t>
+  </si>
+  <si>
+    <t>CAT-005</t>
+  </si>
+  <si>
+    <t>Excessive whitespace inside product cards</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>POSSIBLE REQIREMENTS:</t>
+  </si>
+  <si>
+    <t>Bug 1: Delivery Slot Card Cut Off</t>
+  </si>
+  <si>
+    <t>CHK-DEL-001</t>
+  </si>
+  <si>
+    <t>Checkout</t>
+  </si>
+  <si>
+    <t>Delivery Slot</t>
+  </si>
+  <si>
+    <t>Verify all delivery slots are fully visible on mobile screen</t>
+  </si>
+  <si>
+    <t>All delivery slot options should be completely visible and readable</t>
+  </si>
+  <si>
+    <t>Third delivery slot is partially hidden/cut off on the right side</t>
+  </si>
+  <si>
+    <t>Responsive UI issue</t>
+  </si>
+  <si>
+    <t>Bug 2: Address Showing Google Plus Code</t>
+  </si>
+  <si>
+    <t>CHK-ADR-001</t>
+  </si>
+  <si>
+    <t>Shipping Address</t>
+  </si>
+  <si>
+    <t>Verify shipping address format</t>
+  </si>
+  <si>
+    <t>User-friendly address should be displayed</t>
+  </si>
+  <si>
+    <t>Address starts with "G3XV+W5H" (Google Plus Code)</t>
+  </si>
+  <si>
+    <t>May confuse customers</t>
+  </si>
+  <si>
+    <t>Bug 3: Address Validation Status Misleading</t>
+  </si>
+  <si>
+    <t>CHK-ADR-002</t>
+  </si>
+  <si>
+    <t>Verify address validation status</t>
+  </si>
+  <si>
+    <t>Status should confirm delivery serviceability</t>
+  </si>
+  <si>
+    <t>Displays "Address checked" without showing delivery availability validation</t>
+  </si>
+  <si>
+    <t>Serviceability not clearly communicated</t>
+  </si>
+  <si>
+    <t>Bug 4: Order Summary Hidden Behind Sticky Footer</t>
+  </si>
+  <si>
+    <t>CHK-ORD-001</t>
+  </si>
+  <si>
+    <t>Order Summary</t>
+  </si>
+  <si>
+    <t>Verify complete order summary visibility</t>
+  </si>
+  <si>
+    <t>User should see subtotal, discount, shipping, total amount</t>
+  </si>
+  <si>
+    <t>Sticky footer covers part of Order Summary section</t>
+  </si>
+  <si>
+    <t>User cannot verify bill details</t>
+  </si>
+  <si>
+    <t>Bug 5: Missing Savings Information</t>
+  </si>
+  <si>
+    <t>CHK-ORD-003</t>
+  </si>
+  <si>
+    <t>Discounts</t>
+  </si>
+  <si>
+    <t>Verify savings display</t>
+  </si>
+  <si>
+    <t>Savings should be displayed in Order Summary</t>
+  </si>
+  <si>
+    <t>Discount visible at item level only</t>
+  </si>
+  <si>
+    <t>User cannot see total savings</t>
+  </si>
+  <si>
+    <t>ORD-CONF-001</t>
+  </si>
+  <si>
+    <t>Order Confirmation</t>
+  </si>
+  <si>
+    <t>Payment Status</t>
+  </si>
+  <si>
+    <t>Verify status for Cash/UPI on Delivery orders</t>
+  </si>
+  <si>
+    <t>Status should display "Cash on Delivery" or "Payment on Delivery"</t>
+  </si>
+  <si>
+    <t>Status displays "Payment Pending" even though customer selected Cash/UPI on Delivery</t>
+  </si>
+  <si>
+    <t>Creates confusion and may lead customers to believe payment failed</t>
+  </si>
+  <si>
+    <t>Bug 6:Incorrect Payment Status for COD Orders</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -724,6 +890,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -745,7 +919,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -766,6 +940,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1962,7 +2138,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{051ED67A-7A87-42BF-9B2E-79681FD8C52B}">
-  <dimension ref="A1:K8"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -1976,7 +2152,7 @@
     <col min="11" max="11" width="43.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="50.1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2010,8 +2186,11 @@
       <c r="K1" s="1" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="2" spans="1:11" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L1" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="69.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>82</v>
       </c>
@@ -2045,8 +2224,11 @@
       <c r="K2" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" ht="120" x14ac:dyDescent="0.25">
+      <c r="L2" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>88</v>
       </c>
@@ -2080,8 +2262,11 @@
       <c r="K3" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" ht="90" x14ac:dyDescent="0.25">
+      <c r="L3" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="90" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>86</v>
       </c>
@@ -2115,8 +2300,11 @@
       <c r="K4" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="L4" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>83</v>
       </c>
@@ -2148,8 +2336,11 @@
         <v>17</v>
       </c>
       <c r="K5" s="2"/>
-    </row>
-    <row r="6" spans="1:11" ht="75" x14ac:dyDescent="0.25">
+      <c r="L5" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="75" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>92</v>
       </c>
@@ -2183,8 +2374,11 @@
       <c r="K6" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="135" x14ac:dyDescent="0.25">
+      <c r="L6" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="135" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>94</v>
       </c>
@@ -2218,8 +2412,11 @@
       <c r="K7" s="2" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" ht="60" x14ac:dyDescent="0.25">
+      <c r="L7" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>159</v>
       </c>
@@ -2473,4 +2670,541 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A356BB9-786D-465A-B322-8AD0732DB229}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" customWidth="1"/>
+    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="3" max="3" width="33" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7AAA09CD-F190-4986-BAF6-5ED294D3F6E0}">
+  <dimension ref="A1:I29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" customWidth="1"/>
+    <col min="4" max="4" width="23.42578125" customWidth="1"/>
+    <col min="5" max="5" width="17.7109375" customWidth="1"/>
+    <col min="6" max="6" width="19.42578125" customWidth="1"/>
+    <col min="7" max="7" width="11.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A1" s="9" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="30" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A6" s="9" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A11" s="9" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I13" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A16" s="9" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G18" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H18" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I18" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="75" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A21" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G23" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I23" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" ht="60" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A25" s="2"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+    </row>
+    <row r="26" spans="1:9" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="A26" s="9" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G28" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="H28" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I28" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" ht="135" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>231</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3F7853F-2645-46F7-AA57-0BFFE991D37F}">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="18.42578125" customWidth="1"/>
+    <col min="2" max="2" width="25.28515625" customWidth="1"/>
+    <col min="3" max="3" width="19.85546875" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" customWidth="1"/>
+    <col min="5" max="5" width="19.42578125" customWidth="1"/>
+    <col min="6" max="6" width="21.7109375" customWidth="1"/>
+    <col min="7" max="7" width="17.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" s="8" customFormat="1" ht="31.5" x14ac:dyDescent="0.5">
+      <c r="A1" s="8" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" ht="195" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>